--- a/data/Spatial_resolution_experiment.xlsx
+++ b/data/Spatial_resolution_experiment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lunduniversityo365-my.sharepoint.com/personal/an4718sc_lu_se/Documents/PhD/projects/panama/analyses/spatial_resolution/data/spatial_resolution_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lunduniversityo365-my.sharepoint.com/personal/an4718sc_lu_se/Documents/PhD/projects/panama/analyses/spatial_resolution/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:80_{301222F1-BDD5-774E-BEDF-FBACED2F9920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:80_{0550FBBA-D8A7-3946-BCC4-CFD3A41F72F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="33440" windowHeight="21580" activeTab="4" xr2:uid="{6E41431A-B2E0-E541-802C-2B37FD253AF0}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19160" windowHeight="21600" xr2:uid="{6E41431A-B2E0-E541-802C-2B37FD253AF0}"/>
   </bookViews>
   <sheets>
     <sheet name="maze1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
-    <customWorkbookView name="Andre Scheepers - Personal View" guid="{8A75D892-44B4-104C-BB94-8EB0D0E43396}" mergeInterval="0" personalView="1" maximized="1" yWindow="38" windowWidth="1672" windowHeight="1079" activeSheetId="6"/>
+    <customWorkbookView name="Andre Scheepers - Personal View" guid="{8A75D892-44B4-104C-BB94-8EB0D0E43396}" mergeInterval="0" personalView="1" yWindow="25" windowWidth="1672" windowHeight="1055" activeSheetId="1"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5816" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5816" uniqueCount="804">
   <si>
     <t>ymaze</t>
   </si>
@@ -2460,6 +2460,9 @@
   </si>
   <si>
     <t>C0127_2</t>
+  </si>
+  <si>
+    <t>flight</t>
   </si>
 </sst>
 </file>
@@ -2689,7 +2692,7 @@
 </file>
 
 <file path=xl/revisions/revisionHeaders.xml><?xml version="1.0" encoding="utf-8"?>
-<headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{9AA92E24-C9BD-734B-A564-9966E12B2431}" diskRevisions="1" revisionId="1330" version="7">
+<headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{0D18E071-0B29-D544-95A3-295C7A7411A8}" diskRevisions="1" revisionId="1331" version="9">
   <header guid="{82DA5F4B-74D6-0F4E-8C3A-997C8B5A9649}" dateTime="2024-10-06T17:56:53" maxSheetId="9" userName="Andre Scheepers" r:id="rId1">
     <sheetIdMap count="8">
       <sheetId val="1"/>
@@ -2763,6 +2766,30 @@
     </sheetIdMap>
   </header>
   <header guid="{9AA92E24-C9BD-734B-A564-9966E12B2431}" dateTime="2025-05-05T14:18:46" maxSheetId="9" userName="Andre Scheepers" r:id="rId7" minRId="87" maxRId="1330">
+    <sheetIdMap count="8">
+      <sheetId val="1"/>
+      <sheetId val="2"/>
+      <sheetId val="4"/>
+      <sheetId val="5"/>
+      <sheetId val="6"/>
+      <sheetId val="7"/>
+      <sheetId val="8"/>
+      <sheetId val="3"/>
+    </sheetIdMap>
+  </header>
+  <header guid="{4CC9DF0B-96F7-EF4B-B949-46EED8BDE8AF}" dateTime="2025-07-07T14:58:26" maxSheetId="9" userName="Andre Scheepers" r:id="rId8">
+    <sheetIdMap count="8">
+      <sheetId val="1"/>
+      <sheetId val="2"/>
+      <sheetId val="4"/>
+      <sheetId val="5"/>
+      <sheetId val="6"/>
+      <sheetId val="7"/>
+      <sheetId val="8"/>
+      <sheetId val="3"/>
+    </sheetIdMap>
+  </header>
+  <header guid="{0D18E071-0B29-D544-95A3-295C7A7411A8}" dateTime="2026-09-26T17:36:09" maxSheetId="9" userName="Andre Scheepers" r:id="rId9" minRId="1331">
     <sheetIdMap count="8">
       <sheetId val="1"/>
       <sheetId val="2"/>
@@ -14991,12 +15018,38 @@
 </revisions>
 </file>
 
-<file path=xl/revisions/userNames1.xml><?xml version="1.0" encoding="utf-8"?>
-<users xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" count="4">
+<file path=xl/revisions/revisionLog8.xml><?xml version="1.0" encoding="utf-8"?>
+<revisions xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <rcv guid="{8A75D892-44B4-104C-BB94-8EB0D0E43396}" action="delete"/>
+  <rcv guid="{8A75D892-44B4-104C-BB94-8EB0D0E43396}" action="add"/>
+</revisions>
+</file>
+
+<file path=xl/revisions/revisionLog9.xml><?xml version="1.0" encoding="utf-8"?>
+<revisions xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <rcc rId="1331" sId="1">
+    <oc r="C1" t="inlineStr">
+      <is>
+        <t>bee_flight</t>
+      </is>
+    </oc>
+    <nc r="C1" t="inlineStr">
+      <is>
+        <t>flight</t>
+      </is>
+    </nc>
+  </rcc>
+</revisions>
+</file>
+
+<file path=xl/revisions/userNames.xml><?xml version="1.0" encoding="utf-8"?>
+<users xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" count="6">
   <userInfo guid="{CA1DC199-90D0-B44B-A584-B7049611C0AB}" name="Andre Scheepers" id="-922286283" dateTime="2024-10-06T17:56:53"/>
   <userInfo guid="{CA1DC199-90D0-B44B-A584-B7049611C0AB}" name="Andre Scheepers" id="-922287409" dateTime="2025-02-24T17:20:09"/>
   <userInfo guid="{39621D2D-CD13-4B43-B179-6F3F4790881F}" name="Andre Scheepers" id="-922258916" dateTime="2025-03-13T16:39:40"/>
   <userInfo guid="{9AA92E24-C9BD-734B-A564-9966E12B2431}" name="Andre Scheepers" id="-922249875" dateTime="2025-05-05T14:16:44"/>
+  <userInfo guid="{4CC9DF0B-96F7-EF4B-B949-46EED8BDE8AF}" name="Andre Scheepers" id="-922253428" dateTime="2025-06-06T09:58:27"/>
+  <userInfo guid="{0D18E071-0B29-D544-95A3-295C7A7411A8}" name="Andre Scheepers" id="-922259768" dateTime="2026-09-26T17:31:09"/>
 </users>
 </file>
 
@@ -15295,6 +15348,26 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{6649D996-6833-C548-BBDE-C83189B87AE7}">
+  <we:reference id="93533c7f-4dc5-468f-aba4-1c008e1a7ac8" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200003101" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{135A4D8A-3837-C04D-9096-B7E58473E238}">
   <dimension ref="A1:Y338"/>
@@ -15330,7 +15403,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>803</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -35741,8 +35814,8 @@
   </sortState>
   <customSheetViews>
     <customSheetView guid="{8A75D892-44B4-104C-BB94-8EB0D0E43396}" scale="90">
-      <pane ySplit="1" topLeftCell="A2" activePane="bottomLeft" state="frozen"/>
-      <selection pane="bottomLeft" activeCell="T122" sqref="A1:XFD1048576"/>
+      <pane ySplit="1" topLeftCell="A247" activePane="bottomLeft" state="frozen"/>
+      <selection pane="bottomLeft" activeCell="Q282" sqref="Q282"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
     </customSheetView>
@@ -57836,7 +57909,7 @@
   </sortState>
   <customSheetViews>
     <customSheetView guid="{8A75D892-44B4-104C-BB94-8EB0D0E43396}">
-      <pane ySplit="1" topLeftCell="A48" activePane="bottomLeft" state="frozen"/>
+      <pane ySplit="1" topLeftCell="A2" activePane="bottomLeft" state="frozen"/>
       <selection pane="bottomLeft" activeCell="G73" sqref="G73"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
